--- a/results/job_matches_2026-07-05.xlsx
+++ b/results/job_matches_2026-07-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,41 +567,6 @@
       <c r="G4" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5ab45996cd47738b</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Group AI/ML Sol Architect - PostgreSQL</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>HCLTech</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Virginia Beach, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL, Airflow, Python</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-01-07</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4500ad04a6fe0400</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-05.xlsx
+++ b/results/job_matches_2026-07-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,68 +503,33 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Backend</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AmaWaterways</t>
+          <t>Nicklaus Children's Health System</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, NoSQL, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=02cd4ab61a45abcd</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Nicklaus Children's Health System</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, NoSQL, ETL, ELT, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5ab45996cd47738b</t>
         </is>

--- a/results/job_matches_2026-07-05.xlsx
+++ b/results/job_matches_2026-07-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,41 +497,6 @@
       <c r="G2" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=15009df8a39ab559</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Nicklaus Children's Health System</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, NoSQL, ETL, ELT, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5ab45996cd47738b</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-05.xlsx
+++ b/results/job_matches_2026-07-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,35 +468,105 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Caterpillar</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>AWS, SQS, SNS, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2f34724a0fb298dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>AI Developer and Fintech</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Remote, US USA</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D3" t="n">
         <v>13.2</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, Scala, Oracle, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>2026-07-05</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=15009df8a39ab559</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Engineer II, Data Engineering</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Magnite</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Broomfield, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Spark, Scala, Kafka, ETL, Jenkins, AKS, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f56661e330370a6d</t>
         </is>
       </c>
     </row>
